--- a/VASN/ASNContacts.xlsx
+++ b/VASN/ASNContacts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ex_jmullins\Desktop\Auditor Resources\Calculators\VASN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F185C5E2-D3E4-47C2-A2C7-1F88552295DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5C30B88-D08C-4488-9F2A-E916DFE1A398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{23118619-04CD-4407-B464-1E7DF765F9C0}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{23118619-04CD-4407-B464-1E7DF765F9C0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="25">
   <si>
     <t>OMNMXSAD</t>
   </si>
@@ -123,6 +123,9 @@
   </si>
   <si>
     <t>BEARECYC</t>
+  </si>
+  <si>
+    <t>STRSTEPR</t>
   </si>
 </sst>
 </file>
@@ -184,7 +187,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -214,7 +217,10 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -551,7 +557,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34C17B46-264D-43D9-A20F-D0C47C9E6865}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -612,7 +618,7 @@
       <c r="C4" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="10" t="s">
         <v>19</v>
       </c>
     </row>
@@ -624,7 +630,7 @@
         <v>23</v>
       </c>
       <c r="C5" s="7"/>
-      <c r="D5" s="9"/>
+      <c r="D5" s="10"/>
     </row>
     <row r="6" spans="1:5" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
@@ -634,41 +640,37 @@
         <v>6</v>
       </c>
       <c r="C6" s="8"/>
-      <c r="D6" s="10"/>
-    </row>
-    <row r="7" spans="1:5" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D6" s="11"/>
+    </row>
+    <row r="7" spans="1:5" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>11</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="8"/>
+      <c r="D7" s="11"/>
+    </row>
+    <row r="8" spans="1:5" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="10"/>
-    </row>
-    <row r="8" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>19</v>
-      </c>
+      <c r="C8" s="8"/>
+      <c r="D8" s="11"/>
     </row>
     <row r="9" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>19</v>
@@ -676,31 +678,45 @@
     </row>
     <row r="10" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B11" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C11" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>19</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="C1:C2"/>
-    <mergeCell ref="C4:C7"/>
+    <mergeCell ref="C4:C8"/>
     <mergeCell ref="D1:D2"/>
-    <mergeCell ref="D4:D7"/>
+    <mergeCell ref="D4:D8"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="C9" r:id="rId1" xr:uid="{481C5A78-F15E-47A8-B63E-5B35573D2A31}"/>
+    <hyperlink ref="C10" r:id="rId1" xr:uid="{481C5A78-F15E-47A8-B63E-5B35573D2A31}"/>
     <hyperlink ref="C3" r:id="rId2" xr:uid="{A6E08833-3419-4510-921D-7FAC683C7901}"/>
     <hyperlink ref="C1" r:id="rId3" xr:uid="{AAD8E9A5-08A1-42E3-9A88-2776EECFEBA6}"/>
     <hyperlink ref="C4" r:id="rId4" display="Susan.Riner@fptmetals.com, " xr:uid="{30C9B0F4-80BB-4467-A8A4-6848B455D1BC}"/>
-    <hyperlink ref="C8" r:id="rId5" display="Brittney.Hutson@clevelandcliffs.com" xr:uid="{C83F22CE-55A3-472C-8933-6BC7DDE5CFD3}"/>
+    <hyperlink ref="C9" r:id="rId5" display="Brittney.Hutson@clevelandcliffs.com" xr:uid="{C83F22CE-55A3-472C-8933-6BC7DDE5CFD3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
